--- a/enrollment/fileTemplates/student&sectionTemplates/student(XLSX).xlsx
+++ b/enrollment/fileTemplates/student&sectionTemplates/student(XLSX).xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d725c04a17b73256/Documents/Programming/VSCode/CAPSTONE-preEnrollment/preEnrollmentV6.2/enrollment/fileTemplates/student^0sectionTemplates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A12666A-672B-4379-9E11-03BF66B8A6AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{4A12666A-672B-4379-9E11-03BF66B8A6AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A6F85AC3-BF91-48DD-83B3-49AD521C19C9}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{32C72668-5EA3-4148-AB22-E6FC3855149B}"/>
   </bookViews>
@@ -28,34 +28,34 @@
     <t>Enrolled</t>
   </si>
   <si>
+    <t>1st</t>
+  </si>
+  <si>
+    <t>STUDENT NUMBER</t>
+  </si>
+  <si>
+    <t>FIRST NAME</t>
+  </si>
+  <si>
+    <t>LAST NAME</t>
+  </si>
+  <si>
+    <t>YEAR</t>
+  </si>
+  <si>
+    <t>SECTION</t>
+  </si>
+  <si>
+    <t>SEMESTER</t>
+  </si>
+  <si>
+    <t>STATUS</t>
+  </si>
+  <si>
     <t>Jerry</t>
   </si>
   <si>
     <t>Corazon</t>
-  </si>
-  <si>
-    <t>1st</t>
-  </si>
-  <si>
-    <t>STUDENT NUMBER</t>
-  </si>
-  <si>
-    <t>FIRST NAME</t>
-  </si>
-  <si>
-    <t>LAST NAME</t>
-  </si>
-  <si>
-    <t>YEAR</t>
-  </si>
-  <si>
-    <t>SECTION</t>
-  </si>
-  <si>
-    <t>SEMESTER</t>
-  </si>
-  <si>
-    <t>STATUS</t>
   </si>
 </sst>
 </file>
@@ -935,25 +935,25 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>9</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
@@ -961,10 +961,10 @@
         <v>202310017</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C2" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -973,7 +973,7 @@
         <v>0</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G2" t="s">
         <v>1</v>
